--- a/templates/label_input_template.xlsx
+++ b/templates/label_input_template.xlsx
@@ -141,6 +141,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Insect label maker</author>
+    <author>Pittacia Insectorum</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -148,24 +149,28 @@
         <t>One unique identifier per specimen, stored as text. Printed vertically and encoded in Data Matrix. Example: DEMO000001.</t>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Country display text, for example USA.</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>State/province display text, for example UT. StateProvince is also accepted.</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>County display text, including desired suffix, for example Cache Co.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Short locality for the printed label.</t>
+    <comment ref="B1" authorId="1" shapeId="0">
+      <text>
+        <t>Country display text, for example USA.
+Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with StateProv and County; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="1" shapeId="0">
+      <text>
+        <t>State/province display text, for example UT. StateProvince is also accepted.
+Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with Country and County; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="1" shapeId="0">
+      <text>
+        <t>County display text, including desired suffix, for example Cache Co.
+Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with Country and StateProv; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="1" shapeId="0">
+      <text>
+        <t>Short locality for the printed label.
+Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Uses line 2 by itself. See docs/text_length_guidance.md and check the generated PDF/report.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
@@ -183,29 +188,34 @@
         <t>Meters, numeric; may be blank. The label adds ± and m.</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>Elevation including units, for example 2500m.</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Text exactly as desired on the label, for example 12Jul2026. Include date ranges explicitly.</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>Names as desired for printing. Spaces after initials are condensed automatically.</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>Concise broad habitat. May be blank; field remains present.</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>Concise plant, substrate, or collecting context. May be blank.</t>
+    <comment ref="I1" authorId="1" shapeId="0">
+      <text>
+        <t>Elevation including units, for example 2500m.
+Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 4 with Verbatim_Date and a comma/space. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="1" shapeId="0">
+      <text>
+        <t>Text exactly as desired on the label, for example 12Jul2026. Include date ranges explicitly.
+Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 4 with elevation and a comma/space. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="1" shapeId="0">
+      <text>
+        <t>Names as desired for printing. Spaces after initials are condensed automatically.
+Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Uses line 5. Spaces after initials are removed for display. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="1" shapeId="0">
+      <text>
+        <t>Concise broad habitat. May be blank; field remains present.
+Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 6 with microhabitat at 3.5 pt; may have less room near Field Number. Separate-habitat mode has different limits. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="1" shapeId="0">
+      <text>
+        <t>Concise plant, substrate, or collecting context. May be blank.
+Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 6 with macrohabitat at 3.5 pt; may have less room near Field Number. Separate-habitat mode has different limits. See docs/text_length_guidance.md and check the generated PDF/report.</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
